--- a/outputs/50682.xlsx
+++ b/outputs/50682.xlsx
@@ -437,59 +437,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -838,7 +838,7 @@
       </c>
       <c r="X1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -877,7 +877,7 @@
         <v>20000</v>
       </c>
       <c r="M2" s="5" t="n">
-        <f aca="false">SUMIF(O:O,$A$2,P:P)+SUMIF(Q:Q,$A$2,R:R)+SUMIF(S:S,$A$2,T:T)+SUMIF(U:U,$A$2,V:V)+SUMIF(W:W,$A$2,X:X)</f>
+        <f aca="false">SUMIF(O2:O535,A2,P2:P535)+SUMIF(Q2:Q535,A2,R2:R535)+SUMIF(S2:S535,A2,T2:T535)+SUMIF(U2:U535,A2,V2:V535)+SUMIF(W2:W535,A2,X2:X535)</f>
         <v>9480</v>
       </c>
       <c r="O2" s="1" t="s">
@@ -911,7 +911,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -954,7 +954,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -997,7 +997,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -1040,7 +1040,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1083,7 +1083,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1126,7 +1126,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1169,7 +1169,7 @@
         <v>5040</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1212,7 +1212,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -1255,7 +1255,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1298,7 +1298,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1341,7 +1341,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1384,7 +1384,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1427,7 +1427,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1470,7 +1470,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1513,7 +1513,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1556,7 +1556,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1587,7 +1587,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1618,7 +1618,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1649,7 +1649,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1680,7 +1680,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1711,7 +1711,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1742,7 +1742,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1767,7 +1767,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1786,7 +1786,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -1799,7 +1799,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1812,7 +1812,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -1826,7 +1826,7 @@
       <c r="L28" s="6"/>
       <c r="P28" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -1852,7 +1852,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -1865,7 +1865,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -1891,7 +1891,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -1904,7 +1904,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -1917,7 +1917,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -1930,7 +1930,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -1943,7 +1943,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -1956,7 +1956,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -1969,7 +1969,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
@@ -1982,7 +1982,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
@@ -1995,7 +1995,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -2008,7 +2008,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -2021,7 +2021,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
@@ -2034,7 +2034,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -2047,7 +2047,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -2060,7 +2060,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -2073,7 +2073,7 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -2086,7 +2086,7 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -2099,7 +2099,7 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -2112,7 +2112,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -2125,7 +2125,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -2138,7 +2138,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -2151,7 +2151,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -2167,7 +2167,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
@@ -2183,7 +2183,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -2199,7 +2199,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -2212,7 +2212,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -2225,7 +2225,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -2238,7 +2238,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -2251,7 +2251,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -2264,7 +2264,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -2277,7 +2277,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -2290,7 +2290,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -2303,7 +2303,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -2316,7 +2316,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -2329,7 +2329,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -2342,7 +2342,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -2355,7 +2355,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -2368,7 +2368,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
@@ -2381,7 +2381,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
@@ -2394,7 +2394,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -2407,7 +2407,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
@@ -2420,7 +2420,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
@@ -2433,7 +2433,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
@@ -2446,7 +2446,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
@@ -2459,7 +2459,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
@@ -2472,7 +2472,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
@@ -2485,7 +2485,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
@@ -2498,7 +2498,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
@@ -2511,7 +2511,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
@@ -2524,7 +2524,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
@@ -2537,7 +2537,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
@@ -2550,7 +2550,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
@@ -2563,7 +2563,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
@@ -2576,7 +2576,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
@@ -2589,7 +2589,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
@@ -2602,7 +2602,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
@@ -2615,7 +2615,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
@@ -2628,7 +2628,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
@@ -2641,7 +2641,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
@@ -2654,7 +2654,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
@@ -2667,7 +2667,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
@@ -2680,7 +2680,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -2693,7 +2693,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
@@ -2706,7 +2706,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
@@ -2719,7 +2719,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
@@ -2732,7 +2732,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
@@ -2745,7 +2745,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
@@ -2758,7 +2758,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
@@ -2771,7 +2771,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
@@ -2784,7 +2784,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
@@ -2797,7 +2797,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
@@ -2810,7 +2810,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
@@ -2823,7 +2823,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
@@ -2836,7 +2836,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
@@ -2849,7 +2849,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
@@ -2862,7 +2862,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
@@ -2875,7 +2875,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
@@ -2888,7 +2888,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
@@ -2901,7 +2901,7 @@
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
     </row>
-    <row r="111" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
@@ -2914,7 +2914,7 @@
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
     </row>
-    <row r="112" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
@@ -2927,7 +2927,7 @@
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
     </row>
-    <row r="113" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
@@ -2940,7 +2940,7 @@
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
     </row>
-    <row r="114" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
@@ -2953,7 +2953,7 @@
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
     </row>
-    <row r="115" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
@@ -2966,7 +2966,7 @@
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
     </row>
-    <row r="116" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
@@ -2979,7 +2979,7 @@
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
     </row>
-    <row r="117" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
@@ -2992,7 +2992,7 @@
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
     </row>
-    <row r="118" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
@@ -3005,7 +3005,7 @@
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
     </row>
-    <row r="119" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
@@ -3018,7 +3018,7 @@
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
     </row>
-    <row r="120" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
@@ -3031,7 +3031,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
@@ -3044,7 +3044,7 @@
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
     </row>
-    <row r="122" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
@@ -3057,7 +3057,7 @@
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
     </row>
-    <row r="123" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
@@ -3070,7 +3070,7 @@
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
     </row>
-    <row r="124" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
@@ -3083,7 +3083,7 @@
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
     </row>
-    <row r="125" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
@@ -3096,7 +3096,7 @@
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
     </row>
-    <row r="126" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
@@ -3109,7 +3109,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
@@ -3122,7 +3122,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
       <c r="D128" s="6"/>
@@ -3135,7 +3135,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
@@ -3148,7 +3148,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
@@ -3161,7 +3161,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
       <c r="D131" s="6"/>
@@ -3174,7 +3174,7 @@
       <c r="K131" s="6"/>
       <c r="L131" s="6"/>
     </row>
-    <row r="132" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
       <c r="D132" s="6"/>
@@ -3187,7 +3187,7 @@
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
     </row>
-    <row r="133" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
@@ -3200,7 +3200,7 @@
       <c r="K133" s="6"/>
       <c r="L133" s="6"/>
     </row>
-    <row r="134" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
@@ -3213,7 +3213,7 @@
       <c r="K134" s="6"/>
       <c r="L134" s="6"/>
     </row>
-    <row r="135" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
@@ -3226,7 +3226,7 @@
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
     </row>
-    <row r="136" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
@@ -3239,7 +3239,7 @@
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
     </row>
-    <row r="137" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
@@ -3252,7 +3252,7 @@
       <c r="K137" s="6"/>
       <c r="L137" s="6"/>
     </row>
-    <row r="138" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
       <c r="D138" s="6"/>
@@ -3265,7 +3265,7 @@
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
     </row>
-    <row r="139" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
       <c r="D139" s="6"/>
@@ -3278,7 +3278,7 @@
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
     </row>
-    <row r="140" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
       <c r="D140" s="6"/>
@@ -3291,7 +3291,7 @@
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
     </row>
-    <row r="141" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
@@ -3304,7 +3304,7 @@
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
     </row>
-    <row r="142" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
       <c r="D142" s="6"/>
@@ -3317,7 +3317,7 @@
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
     </row>
-    <row r="143" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
@@ -3330,7 +3330,7 @@
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
     </row>
-    <row r="144" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
       <c r="D144" s="6"/>
@@ -3343,7 +3343,7 @@
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
     </row>
-    <row r="145" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
       <c r="D145" s="6"/>
@@ -3356,7 +3356,7 @@
       <c r="K145" s="6"/>
       <c r="L145" s="6"/>
     </row>
-    <row r="146" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
@@ -3369,7 +3369,7 @@
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
     </row>
-    <row r="147" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
       <c r="D147" s="6"/>
@@ -3382,7 +3382,7 @@
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
     </row>
-    <row r="148" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
       <c r="D148" s="6"/>
@@ -3395,7 +3395,7 @@
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
     </row>
-    <row r="149" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
@@ -3408,7 +3408,7 @@
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
     </row>
-    <row r="150" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
@@ -3421,7 +3421,7 @@
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
     </row>
-    <row r="151" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
@@ -3434,7 +3434,7 @@
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
     </row>
-    <row r="152" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -3447,7 +3447,7 @@
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
     </row>
-    <row r="153" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
@@ -3460,7 +3460,7 @@
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
     </row>
-    <row r="154" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
@@ -3473,7 +3473,7 @@
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
     </row>
-    <row r="155" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
@@ -3486,7 +3486,7 @@
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
     </row>
-    <row r="156" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
@@ -3499,7 +3499,7 @@
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
     </row>
-    <row r="157" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
@@ -3512,7 +3512,7 @@
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
     </row>
-    <row r="158" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
@@ -3525,7 +3525,7 @@
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
     </row>
-    <row r="159" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
@@ -3538,7 +3538,7 @@
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
     </row>
-    <row r="160" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
       <c r="D160" s="6"/>
@@ -3551,7 +3551,7 @@
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
     </row>
-    <row r="161" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
       <c r="D161" s="6"/>
@@ -3564,7 +3564,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
       <c r="D162" s="6"/>
@@ -3577,7 +3577,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
@@ -3590,7 +3590,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
@@ -3603,7 +3603,7 @@
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
     </row>
-    <row r="165" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
@@ -3616,7 +3616,7 @@
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
     </row>
-    <row r="166" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
@@ -3629,7 +3629,7 @@
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
     </row>
-    <row r="167" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
@@ -3642,7 +3642,7 @@
       <c r="K167" s="6"/>
       <c r="L167" s="6"/>
     </row>
-    <row r="168" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
@@ -3655,7 +3655,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
@@ -3668,7 +3668,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="13"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -3682,7 +3682,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="13"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -3696,7 +3696,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="13"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -3710,7 +3710,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="13"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -3724,7 +3724,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="13"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -3738,7 +3738,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="13"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -3752,7 +3752,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="13"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -3766,7 +3766,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="13"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -3780,7 +3780,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="13"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -3794,7 +3794,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="13"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -3808,7 +3808,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="13"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -3822,7 +3822,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="13"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -3836,7 +3836,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="13"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -3850,7 +3850,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="13"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -3864,7 +3864,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="13"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -3878,7 +3878,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="13"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -3892,7 +3892,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="13"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -3906,7 +3906,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="13"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -3920,7 +3920,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="13"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -3934,7 +3934,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="13"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -3948,7 +3948,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="13"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -3962,7 +3962,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="13"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -3976,7 +3976,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="13"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -3990,7 +3990,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="13"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -4004,7 +4004,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="13"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -4018,7 +4018,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="13"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -4032,7 +4032,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="13"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -4046,7 +4046,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="13"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -4060,7 +4060,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="13"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -4074,7 +4074,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="13"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -4088,7 +4088,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="13"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
@@ -4102,7 +4102,7 @@
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
     </row>
-    <row r="201" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="13"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
@@ -4116,7 +4116,7 @@
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
     </row>
-    <row r="202" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="13"/>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -4130,7 +4130,7 @@
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
     </row>
-    <row r="203" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="13"/>
       <c r="B203" s="6"/>
       <c r="C203" s="6"/>
@@ -4144,7 +4144,7 @@
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
     </row>
-    <row r="204" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="13"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
@@ -4158,7 +4158,7 @@
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
     </row>
-    <row r="205" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="13"/>
       <c r="B205" s="6"/>
       <c r="C205" s="6"/>
@@ -4172,7 +4172,7 @@
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
     </row>
-    <row r="206" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="13"/>
       <c r="B206" s="6"/>
       <c r="C206" s="6"/>
@@ -4186,7 +4186,7 @@
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
     </row>
-    <row r="207" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="13"/>
       <c r="B207" s="6"/>
       <c r="C207" s="6"/>
@@ -4200,7 +4200,7 @@
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
     </row>
-    <row r="208" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="13"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6"/>
@@ -4214,7 +4214,7 @@
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
     </row>
-    <row r="209" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="13"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6"/>
@@ -4228,7 +4228,7 @@
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
     </row>
-    <row r="210" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="13"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6"/>
@@ -4242,7 +4242,7 @@
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
     </row>
-    <row r="211" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="13"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
@@ -4256,7 +4256,7 @@
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
     </row>
-    <row r="212" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="13"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
@@ -4270,7 +4270,7 @@
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
     </row>
-    <row r="213" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="13"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6"/>
@@ -4284,7 +4284,7 @@
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
     </row>
-    <row r="214" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="13"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
@@ -4298,7 +4298,7 @@
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
     </row>
-    <row r="215" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="13"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6"/>
@@ -4312,7 +4312,7 @@
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
     </row>
-    <row r="216" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="13"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6"/>
@@ -4326,7 +4326,7 @@
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
     </row>
-    <row r="217" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="13"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6"/>
@@ -4340,7 +4340,7 @@
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
     </row>
-    <row r="218" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="13"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6"/>
@@ -4354,7 +4354,7 @@
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
     </row>
-    <row r="219" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="13"/>
       <c r="B219" s="6"/>
       <c r="C219" s="6"/>
@@ -4368,7 +4368,7 @@
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
     </row>
-    <row r="220" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="13"/>
       <c r="B220" s="6"/>
       <c r="C220" s="6"/>
@@ -4382,7 +4382,7 @@
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
     </row>
-    <row r="221" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="13"/>
       <c r="B221" s="6"/>
       <c r="C221" s="6"/>
@@ -4396,7 +4396,7 @@
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
     </row>
-    <row r="222" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="13"/>
       <c r="B222" s="6"/>
       <c r="C222" s="6"/>
@@ -4410,7 +4410,7 @@
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
     </row>
-    <row r="223" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="13"/>
       <c r="B223" s="6"/>
       <c r="C223" s="6"/>
@@ -4424,7 +4424,7 @@
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
     </row>
-    <row r="224" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="13"/>
       <c r="B224" s="6"/>
       <c r="C224" s="6"/>
@@ -4438,7 +4438,7 @@
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
     </row>
-    <row r="225" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="13"/>
       <c r="B225" s="6"/>
       <c r="C225" s="6"/>
@@ -4452,7 +4452,7 @@
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
     </row>
-    <row r="226" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="13"/>
       <c r="B226" s="6"/>
       <c r="C226" s="6"/>
@@ -4466,7 +4466,7 @@
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
     </row>
-    <row r="227" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="13"/>
       <c r="B227" s="6"/>
       <c r="C227" s="6"/>
@@ -4480,7 +4480,7 @@
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
     </row>
-    <row r="228" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="13"/>
       <c r="B228" s="6"/>
       <c r="C228" s="6"/>
@@ -4494,7 +4494,7 @@
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
     </row>
-    <row r="229" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="13"/>
       <c r="B229" s="6"/>
       <c r="C229" s="6"/>
@@ -4508,7 +4508,7 @@
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
     </row>
-    <row r="230" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="13"/>
       <c r="B230" s="6"/>
       <c r="C230" s="6"/>
@@ -4522,7 +4522,7 @@
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
     </row>
-    <row r="231" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="13"/>
       <c r="B231" s="6"/>
       <c r="C231" s="6"/>
@@ -4536,7 +4536,7 @@
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
     </row>
-    <row r="232" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="13"/>
       <c r="B232" s="6"/>
       <c r="C232" s="6"/>
@@ -4550,7 +4550,7 @@
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
     </row>
-    <row r="233" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="13"/>
       <c r="B233" s="6"/>
       <c r="C233" s="6"/>
@@ -4564,7 +4564,7 @@
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
     </row>
-    <row r="234" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="13"/>
       <c r="B234" s="6"/>
       <c r="C234" s="6"/>
@@ -4578,7 +4578,7 @@
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
     </row>
-    <row r="235" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="13"/>
       <c r="B235" s="6"/>
       <c r="C235" s="6"/>
@@ -4592,7 +4592,7 @@
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
     </row>
-    <row r="236" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="13"/>
       <c r="B236" s="6"/>
       <c r="C236" s="6"/>
@@ -4606,7 +4606,7 @@
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
     </row>
-    <row r="237" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="13"/>
       <c r="B237" s="6"/>
       <c r="C237" s="6"/>
@@ -4620,7 +4620,7 @@
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
     </row>
-    <row r="238" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="13"/>
       <c r="B238" s="6"/>
       <c r="C238" s="6"/>
@@ -4634,7 +4634,7 @@
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
     </row>
-    <row r="239" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="13"/>
       <c r="B239" s="6"/>
       <c r="C239" s="6"/>
@@ -4648,7 +4648,7 @@
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
     </row>
-    <row r="240" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="13"/>
       <c r="B240" s="6"/>
       <c r="C240" s="6"/>
@@ -4662,7 +4662,7 @@
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
     </row>
-    <row r="241" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="13"/>
       <c r="B241" s="6"/>
       <c r="C241" s="6"/>
@@ -4676,7 +4676,7 @@
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
     </row>
-    <row r="242" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="13"/>
       <c r="B242" s="6"/>
       <c r="C242" s="6"/>
@@ -4690,7 +4690,7 @@
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
     </row>
-    <row r="243" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="13"/>
       <c r="B243" s="6"/>
       <c r="C243" s="6"/>
@@ -4704,7 +4704,7 @@
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
     </row>
-    <row r="244" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="13"/>
       <c r="B244" s="6"/>
       <c r="C244" s="6"/>
@@ -4718,7 +4718,7 @@
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
     </row>
-    <row r="245" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="13"/>
       <c r="B245" s="6"/>
       <c r="C245" s="6"/>
@@ -4732,7 +4732,7 @@
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
     </row>
-    <row r="246" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="13"/>
       <c r="B246" s="6"/>
       <c r="C246" s="6"/>
@@ -4746,7 +4746,7 @@
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
     </row>
-    <row r="247" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="13"/>
       <c r="B247" s="6"/>
       <c r="C247" s="6"/>
@@ -4760,7 +4760,7 @@
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
     </row>
-    <row r="248" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="13"/>
       <c r="B248" s="6"/>
       <c r="C248" s="6"/>
@@ -4774,7 +4774,7 @@
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
     </row>
-    <row r="249" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="13"/>
       <c r="B249" s="6"/>
       <c r="C249" s="6"/>
@@ -4788,7 +4788,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
     </row>
-    <row r="250" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="13"/>
       <c r="B250" s="6"/>
       <c r="C250" s="6"/>
@@ -4802,7 +4802,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
     </row>
-    <row r="251" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="13"/>
       <c r="B251" s="6"/>
       <c r="C251" s="6"/>
@@ -4816,7 +4816,7 @@
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
     </row>
-    <row r="252" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="13"/>
       <c r="B252" s="6"/>
       <c r="C252" s="6"/>
@@ -4830,7 +4830,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
     </row>
-    <row r="253" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="13"/>
       <c r="B253" s="6"/>
       <c r="C253" s="6"/>
@@ -4844,7 +4844,7 @@
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
     </row>
-    <row r="254" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="13"/>
       <c r="B254" s="6"/>
       <c r="C254" s="6"/>
@@ -4858,7 +4858,7 @@
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
     </row>
-    <row r="255" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="13"/>
       <c r="B255" s="6"/>
       <c r="C255" s="6"/>
@@ -4872,7 +4872,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
     </row>
-    <row r="256" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="13"/>
       <c r="B256" s="6"/>
       <c r="C256" s="6"/>
@@ -4886,7 +4886,7 @@
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
     </row>
-    <row r="257" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="13"/>
       <c r="B257" s="6"/>
       <c r="C257" s="6"/>
@@ -4900,7 +4900,7 @@
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
     </row>
-    <row r="258" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="13"/>
       <c r="B258" s="6"/>
       <c r="C258" s="6"/>
@@ -4914,7 +4914,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
     </row>
-    <row r="259" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="13"/>
       <c r="B259" s="6"/>
       <c r="C259" s="6"/>
@@ -4928,7 +4928,7 @@
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
     </row>
-    <row r="260" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="13"/>
       <c r="B260" s="6"/>
       <c r="C260" s="6"/>
@@ -4942,7 +4942,7 @@
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
     </row>
-    <row r="261" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="13"/>
       <c r="B261" s="6"/>
       <c r="C261" s="6"/>
@@ -4956,7 +4956,7 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
     </row>
-    <row r="262" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="13"/>
       <c r="B262" s="6"/>
       <c r="C262" s="6"/>
@@ -4970,7 +4970,7 @@
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
     </row>
-    <row r="263" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="13"/>
       <c r="B263" s="6"/>
       <c r="C263" s="6"/>
@@ -4984,7 +4984,7 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
     </row>
-    <row r="264" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="13"/>
       <c r="B264" s="6"/>
       <c r="C264" s="6"/>
@@ -4998,7 +4998,7 @@
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
     </row>
-    <row r="265" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="13"/>
       <c r="B265" s="6"/>
       <c r="C265" s="6"/>
@@ -5012,7 +5012,7 @@
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
     </row>
-    <row r="266" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="13"/>
       <c r="B266" s="6"/>
       <c r="C266" s="6"/>
@@ -5026,7 +5026,7 @@
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
     </row>
-    <row r="267" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="13"/>
       <c r="B267" s="6"/>
       <c r="C267" s="6"/>
@@ -5040,7 +5040,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
     </row>
-    <row r="268" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="13"/>
       <c r="B268" s="6"/>
       <c r="C268" s="6"/>
@@ -5054,7 +5054,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
     </row>
-    <row r="269" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="13"/>
       <c r="B269" s="6"/>
       <c r="C269" s="6"/>
@@ -5068,7 +5068,7 @@
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
     </row>
-    <row r="270" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="13"/>
       <c r="B270" s="6"/>
       <c r="C270" s="6"/>
@@ -5082,7 +5082,7 @@
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
     </row>
-    <row r="271" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="13"/>
       <c r="B271" s="6"/>
       <c r="C271" s="6"/>
@@ -5096,7 +5096,7 @@
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
     </row>
-    <row r="272" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="13"/>
       <c r="B272" s="6"/>
       <c r="C272" s="6"/>
@@ -5110,7 +5110,7 @@
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
     </row>
-    <row r="273" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="13"/>
       <c r="B273" s="6"/>
       <c r="C273" s="6"/>
@@ -5124,7 +5124,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
     </row>
-    <row r="274" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="13"/>
       <c r="B274" s="6"/>
       <c r="C274" s="6"/>
@@ -5138,7 +5138,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
     </row>
-    <row r="275" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="13"/>
       <c r="B275" s="6"/>
       <c r="C275" s="6"/>
@@ -5152,7 +5152,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
     </row>
-    <row r="276" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="13"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6"/>
@@ -5166,7 +5166,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
     </row>
-    <row r="277" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="13"/>
       <c r="B277" s="6"/>
       <c r="C277" s="6"/>
@@ -5180,7 +5180,7 @@
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
     </row>
-    <row r="278" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="13"/>
       <c r="B278" s="6"/>
       <c r="C278" s="6"/>
@@ -5194,7 +5194,7 @@
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
     </row>
-    <row r="279" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="13"/>
       <c r="B279" s="6"/>
       <c r="C279" s="6"/>
@@ -5208,7 +5208,7 @@
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
     </row>
-    <row r="280" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="13"/>
       <c r="B280" s="6"/>
       <c r="C280" s="6"/>
@@ -5222,7 +5222,7 @@
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
     </row>
-    <row r="281" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="13"/>
       <c r="B281" s="6"/>
       <c r="C281" s="6"/>
@@ -5236,7 +5236,7 @@
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
     </row>
-    <row r="282" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="13"/>
       <c r="B282" s="6"/>
       <c r="C282" s="6"/>
@@ -5250,7 +5250,7 @@
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
     </row>
-    <row r="283" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="13"/>
       <c r="B283" s="6"/>
       <c r="C283" s="6"/>
@@ -5264,7 +5264,7 @@
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
     </row>
-    <row r="284" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="13"/>
       <c r="B284" s="6"/>
       <c r="C284" s="6"/>
@@ -5278,7 +5278,7 @@
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
     </row>
-    <row r="285" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="13"/>
       <c r="B285" s="6"/>
       <c r="C285" s="6"/>
@@ -5292,7 +5292,7 @@
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
     </row>
-    <row r="286" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="13"/>
       <c r="B286" s="6"/>
       <c r="C286" s="6"/>
@@ -5306,7 +5306,7 @@
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
     </row>
-    <row r="287" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="13"/>
       <c r="B287" s="6"/>
       <c r="C287" s="6"/>
@@ -5320,7 +5320,7 @@
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
     </row>
-    <row r="288" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="13"/>
       <c r="B288" s="6"/>
       <c r="C288" s="6"/>
@@ -5334,7 +5334,7 @@
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
     </row>
-    <row r="289" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="13"/>
       <c r="B289" s="6"/>
       <c r="C289" s="6"/>
@@ -5348,7 +5348,7 @@
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
     </row>
-    <row r="290" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="13"/>
       <c r="B290" s="6"/>
       <c r="C290" s="6"/>
@@ -5362,7 +5362,7 @@
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
     </row>
-    <row r="291" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="13"/>
       <c r="B291" s="6"/>
       <c r="C291" s="6"/>
@@ -5376,7 +5376,7 @@
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
     </row>
-    <row r="292" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="13"/>
       <c r="B292" s="6"/>
       <c r="C292" s="6"/>
@@ -5390,7 +5390,7 @@
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
     </row>
-    <row r="293" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="13"/>
       <c r="B293" s="6"/>
       <c r="C293" s="6"/>
@@ -5404,7 +5404,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
     </row>
-    <row r="294" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="13"/>
       <c r="B294" s="6"/>
       <c r="C294" s="6"/>
@@ -5418,7 +5418,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
     </row>
-    <row r="295" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="13"/>
       <c r="B295" s="6"/>
       <c r="C295" s="6"/>
@@ -5432,7 +5432,7 @@
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
     </row>
-    <row r="296" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="13"/>
       <c r="B296" s="6"/>
       <c r="C296" s="6"/>
@@ -5446,7 +5446,7 @@
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
     </row>
-    <row r="297" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="13"/>
       <c r="B297" s="6"/>
       <c r="C297" s="6"/>
@@ -5460,7 +5460,7 @@
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
     </row>
-    <row r="298" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="13"/>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -5474,7 +5474,7 @@
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
     </row>
-    <row r="299" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="13"/>
       <c r="B299" s="6"/>
       <c r="C299" s="6"/>
@@ -5488,7 +5488,7 @@
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
     </row>
-    <row r="300" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="13"/>
       <c r="B300" s="6"/>
       <c r="C300" s="6"/>
@@ -5502,7 +5502,7 @@
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
     </row>
-    <row r="301" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="13"/>
       <c r="B301" s="6"/>
       <c r="C301" s="6"/>
@@ -5516,7 +5516,7 @@
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
     </row>
-    <row r="302" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="13"/>
       <c r="B302" s="6"/>
       <c r="C302" s="6"/>
@@ -5530,7 +5530,7 @@
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
     </row>
-    <row r="303" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="13"/>
       <c r="B303" s="6"/>
       <c r="C303" s="6"/>
@@ -5544,7 +5544,7 @@
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
     </row>
-    <row r="304" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="13"/>
       <c r="B304" s="6"/>
       <c r="C304" s="6"/>
@@ -5558,7 +5558,7 @@
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
     </row>
-    <row r="305" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="13"/>
       <c r="B305" s="6"/>
       <c r="C305" s="6"/>
@@ -5572,7 +5572,7 @@
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
     </row>
-    <row r="306" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="13"/>
       <c r="B306" s="6"/>
       <c r="C306" s="6"/>
@@ -5586,7 +5586,7 @@
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
     </row>
-    <row r="307" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="13"/>
       <c r="B307" s="6"/>
       <c r="C307" s="6"/>
@@ -5600,7 +5600,7 @@
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
     </row>
-    <row r="308" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="13"/>
       <c r="B308" s="6"/>
       <c r="C308" s="6"/>
@@ -5614,7 +5614,7 @@
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
     </row>
-    <row r="309" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="13"/>
       <c r="B309" s="6"/>
       <c r="C309" s="6"/>
@@ -5628,7 +5628,7 @@
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
     </row>
-    <row r="310" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="13"/>
       <c r="B310" s="6"/>
       <c r="C310" s="6"/>
@@ -5642,7 +5642,7 @@
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
     </row>
-    <row r="311" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="13"/>
       <c r="B311" s="6"/>
       <c r="C311" s="6"/>
@@ -5656,7 +5656,7 @@
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
     </row>
-    <row r="312" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="13"/>
       <c r="B312" s="6"/>
       <c r="C312" s="6"/>
@@ -5670,7 +5670,7 @@
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
     </row>
-    <row r="313" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="13"/>
       <c r="B313" s="6"/>
       <c r="C313" s="6"/>
@@ -5684,7 +5684,7 @@
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
     </row>
-    <row r="314" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="13"/>
       <c r="B314" s="6"/>
       <c r="C314" s="6"/>
@@ -5698,7 +5698,7 @@
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
     </row>
-    <row r="315" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="13"/>
       <c r="B315" s="6"/>
       <c r="C315" s="6"/>
@@ -5712,7 +5712,7 @@
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
     </row>
-    <row r="316" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="13"/>
       <c r="B316" s="6"/>
       <c r="C316" s="6"/>
@@ -5726,7 +5726,7 @@
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
     </row>
-    <row r="317" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="13"/>
       <c r="B317" s="6"/>
       <c r="C317" s="6"/>
@@ -5740,7 +5740,7 @@
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
     </row>
-    <row r="318" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="13"/>
       <c r="B318" s="6"/>
       <c r="C318" s="6"/>
@@ -5754,7 +5754,7 @@
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
     </row>
-    <row r="319" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="13"/>
       <c r="B319" s="6"/>
       <c r="C319" s="6"/>
@@ -5768,7 +5768,7 @@
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
     </row>
-    <row r="320" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="13"/>
       <c r="B320" s="6"/>
       <c r="C320" s="6"/>
@@ -5782,7 +5782,7 @@
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
     </row>
-    <row r="321" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="13"/>
       <c r="B321" s="6"/>
       <c r="C321" s="6"/>
@@ -5796,7 +5796,7 @@
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
     </row>
-    <row r="322" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="13"/>
       <c r="B322" s="6"/>
       <c r="C322" s="6"/>
@@ -5810,7 +5810,7 @@
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
     </row>
-    <row r="323" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="13"/>
       <c r="B323" s="6"/>
       <c r="C323" s="6"/>
@@ -5824,7 +5824,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
     </row>
-    <row r="324" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="13"/>
       <c r="B324" s="6"/>
       <c r="C324" s="6"/>
@@ -5838,7 +5838,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
     </row>
-    <row r="325" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="13"/>
       <c r="B325" s="6"/>
       <c r="C325" s="6"/>
@@ -5852,7 +5852,7 @@
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
     </row>
-    <row r="326" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="13"/>
       <c r="B326" s="6"/>
       <c r="C326" s="6"/>
@@ -5866,7 +5866,7 @@
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
     </row>
-    <row r="327" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="13"/>
       <c r="B327" s="6"/>
       <c r="C327" s="6"/>
@@ -5880,7 +5880,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
     </row>
-    <row r="328" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="13"/>
       <c r="B328" s="6"/>
       <c r="C328" s="6"/>
@@ -5894,7 +5894,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
     </row>
-    <row r="329" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="13"/>
       <c r="B329" s="6"/>
       <c r="C329" s="6"/>
@@ -5908,7 +5908,7 @@
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
     </row>
-    <row r="330" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="13"/>
       <c r="B330" s="6"/>
       <c r="C330" s="6"/>
@@ -5922,7 +5922,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
     </row>
-    <row r="331" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="13"/>
       <c r="B331" s="6"/>
       <c r="C331" s="6"/>
@@ -5936,7 +5936,7 @@
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
     </row>
-    <row r="332" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="13"/>
       <c r="B332" s="6"/>
       <c r="C332" s="6"/>
@@ -5950,7 +5950,7 @@
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
     </row>
-    <row r="333" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="13"/>
       <c r="B333" s="6"/>
       <c r="C333" s="6"/>
@@ -5964,7 +5964,7 @@
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
     </row>
-    <row r="334" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="13"/>
       <c r="B334" s="6"/>
       <c r="C334" s="6"/>
@@ -5978,7 +5978,7 @@
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
     </row>
-    <row r="335" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="13"/>
       <c r="B335" s="6"/>
       <c r="C335" s="6"/>
@@ -5992,7 +5992,7 @@
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
     </row>
-    <row r="336" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="13"/>
       <c r="B336" s="6"/>
       <c r="C336" s="6"/>
@@ -6006,7 +6006,7 @@
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
     </row>
-    <row r="337" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="13"/>
       <c r="B337" s="6"/>
       <c r="C337" s="6"/>
@@ -6020,7 +6020,7 @@
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
     </row>
-    <row r="338" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="13"/>
       <c r="B338" s="6"/>
       <c r="C338" s="6"/>
@@ -6034,7 +6034,7 @@
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
     </row>
-    <row r="339" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="13"/>
       <c r="B339" s="6"/>
       <c r="C339" s="6"/>
@@ -6048,7 +6048,7 @@
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
     </row>
-    <row r="340" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="13"/>
       <c r="B340" s="6"/>
       <c r="C340" s="6"/>
@@ -6062,7 +6062,7 @@
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
     </row>
-    <row r="341" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="13"/>
       <c r="B341" s="6"/>
       <c r="C341" s="6"/>
@@ -6076,7 +6076,7 @@
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
     </row>
-    <row r="342" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="13"/>
       <c r="B342" s="6"/>
       <c r="C342" s="6"/>
@@ -6090,7 +6090,7 @@
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
     </row>
-    <row r="343" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="13"/>
       <c r="B343" s="6"/>
       <c r="C343" s="6"/>
@@ -6104,7 +6104,7 @@
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
     </row>
-    <row r="344" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="13"/>
       <c r="B344" s="6"/>
       <c r="C344" s="6"/>
@@ -6118,7 +6118,7 @@
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
     </row>
-    <row r="345" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="13"/>
       <c r="B345" s="6"/>
       <c r="C345" s="6"/>
@@ -6132,7 +6132,7 @@
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
     </row>
-    <row r="346" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="13"/>
       <c r="B346" s="6"/>
       <c r="C346" s="6"/>
@@ -6146,7 +6146,7 @@
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
     </row>
-    <row r="347" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="13"/>
       <c r="B347" s="6"/>
       <c r="C347" s="6"/>
@@ -6160,7 +6160,7 @@
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
     </row>
-    <row r="348" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="13"/>
       <c r="B348" s="6"/>
       <c r="C348" s="6"/>
@@ -6174,7 +6174,7 @@
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
     </row>
-    <row r="349" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="13"/>
       <c r="B349" s="6"/>
       <c r="C349" s="6"/>
@@ -6188,7 +6188,7 @@
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
     </row>
-    <row r="350" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="13"/>
       <c r="B350" s="6"/>
       <c r="C350" s="6"/>
@@ -6202,7 +6202,7 @@
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
     </row>
-    <row r="351" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="13"/>
       <c r="B351" s="6"/>
       <c r="C351" s="6"/>
@@ -6216,7 +6216,7 @@
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
     </row>
-    <row r="352" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="13"/>
       <c r="B352" s="6"/>
       <c r="C352" s="6"/>
@@ -6230,7 +6230,7 @@
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
     </row>
-    <row r="353" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="13"/>
       <c r="B353" s="6"/>
       <c r="C353" s="6"/>
@@ -6244,7 +6244,7 @@
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
     </row>
-    <row r="354" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="13"/>
       <c r="B354" s="6"/>
       <c r="C354" s="6"/>
@@ -6258,7 +6258,7 @@
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
     </row>
-    <row r="355" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="13"/>
       <c r="B355" s="6"/>
       <c r="C355" s="6"/>
@@ -6272,7 +6272,7 @@
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
     </row>
-    <row r="356" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="13"/>
       <c r="B356" s="6"/>
       <c r="C356" s="6"/>
@@ -6286,7 +6286,7 @@
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
     </row>
-    <row r="357" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="13"/>
       <c r="B357" s="6"/>
       <c r="C357" s="6"/>
@@ -6300,7 +6300,7 @@
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
     </row>
-    <row r="358" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="13"/>
       <c r="B358" s="6"/>
       <c r="C358" s="6"/>
@@ -6314,7 +6314,7 @@
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
     </row>
-    <row r="359" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="13"/>
       <c r="B359" s="6"/>
       <c r="C359" s="6"/>
@@ -6328,7 +6328,7 @@
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
     </row>
-    <row r="360" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="13"/>
       <c r="B360" s="6"/>
       <c r="C360" s="6"/>
@@ -6342,7 +6342,7 @@
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
     </row>
-    <row r="361" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="13"/>
       <c r="B361" s="6"/>
       <c r="C361" s="6"/>
@@ -6356,7 +6356,7 @@
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
     </row>
-    <row r="362" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="13"/>
       <c r="B362" s="6"/>
       <c r="C362" s="6"/>
@@ -6370,7 +6370,7 @@
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
     </row>
-    <row r="363" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="13"/>
       <c r="B363" s="6"/>
       <c r="C363" s="6"/>
@@ -6384,7 +6384,7 @@
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
     </row>
-    <row r="364" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="13"/>
       <c r="B364" s="6"/>
       <c r="C364" s="6"/>
@@ -6398,7 +6398,7 @@
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
     </row>
-    <row r="365" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="13"/>
       <c r="B365" s="6"/>
       <c r="C365" s="6"/>
@@ -6412,7 +6412,7 @@
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
     </row>
-    <row r="366" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="13"/>
       <c r="B366" s="6"/>
       <c r="C366" s="6"/>
@@ -6426,7 +6426,7 @@
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
     </row>
-    <row r="367" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="13"/>
       <c r="B367" s="6"/>
       <c r="C367" s="6"/>
@@ -6440,7 +6440,7 @@
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
     </row>
-    <row r="368" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="13"/>
       <c r="B368" s="6"/>
       <c r="C368" s="6"/>
@@ -6454,7 +6454,7 @@
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
     </row>
-    <row r="369" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="13"/>
       <c r="B369" s="6"/>
       <c r="C369" s="6"/>
@@ -6468,7 +6468,7 @@
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
     </row>
-    <row r="370" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="13"/>
       <c r="B370" s="6"/>
       <c r="C370" s="6"/>
@@ -6482,7 +6482,7 @@
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
     </row>
-    <row r="371" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="13"/>
       <c r="B371" s="6"/>
       <c r="C371" s="6"/>
@@ -6496,7 +6496,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
     </row>
-    <row r="372" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="13"/>
       <c r="B372" s="6"/>
       <c r="C372" s="6"/>
@@ -6510,7 +6510,7 @@
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
     </row>
-    <row r="373" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="13"/>
       <c r="B373" s="6"/>
       <c r="C373" s="6"/>
@@ -6524,7 +6524,7 @@
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
     </row>
-    <row r="374" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="13"/>
       <c r="B374" s="6"/>
       <c r="C374" s="6"/>
@@ -6538,7 +6538,7 @@
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
     </row>
-    <row r="375" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="13"/>
       <c r="B375" s="6"/>
       <c r="C375" s="6"/>
@@ -6552,7 +6552,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
     </row>
-    <row r="376" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="13"/>
       <c r="B376" s="6"/>
       <c r="C376" s="6"/>
@@ -6566,7 +6566,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
     </row>
-    <row r="377" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="13"/>
       <c r="B377" s="6"/>
       <c r="C377" s="6"/>
@@ -6580,7 +6580,7 @@
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
     </row>
-    <row r="378" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="13"/>
       <c r="B378" s="6"/>
       <c r="C378" s="6"/>
@@ -6594,7 +6594,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
     </row>
-    <row r="379" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="13"/>
       <c r="B379" s="6"/>
       <c r="C379" s="6"/>
@@ -6608,7 +6608,7 @@
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
     </row>
-    <row r="380" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="13"/>
       <c r="B380" s="6"/>
       <c r="C380" s="6"/>
@@ -6622,7 +6622,7 @@
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
     </row>
-    <row r="381" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="13"/>
       <c r="B381" s="6"/>
       <c r="C381" s="6"/>
@@ -6636,7 +6636,7 @@
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
     </row>
-    <row r="382" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="13"/>
       <c r="B382" s="6"/>
       <c r="C382" s="6"/>
@@ -6650,7 +6650,7 @@
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
     </row>
-    <row r="383" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="13"/>
       <c r="B383" s="6"/>
       <c r="C383" s="6"/>
@@ -6664,7 +6664,7 @@
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
     </row>
-    <row r="384" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="13"/>
       <c r="B384" s="6"/>
       <c r="C384" s="6"/>
@@ -6678,7 +6678,7 @@
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
     </row>
-    <row r="385" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="13"/>
       <c r="B385" s="6"/>
       <c r="C385" s="6"/>
@@ -6692,7 +6692,7 @@
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
     </row>
-    <row r="386" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="13"/>
       <c r="B386" s="6"/>
       <c r="C386" s="6"/>
@@ -6706,7 +6706,7 @@
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
     </row>
-    <row r="387" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="13"/>
       <c r="B387" s="6"/>
       <c r="C387" s="6"/>
@@ -6720,7 +6720,7 @@
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
     </row>
-    <row r="388" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="13"/>
       <c r="B388" s="6"/>
       <c r="C388" s="6"/>
@@ -6734,7 +6734,7 @@
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
     </row>
-    <row r="389" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="13"/>
       <c r="B389" s="6"/>
       <c r="C389" s="6"/>
@@ -6748,7 +6748,7 @@
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
     </row>
-    <row r="390" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="13"/>
       <c r="B390" s="6"/>
       <c r="C390" s="6"/>
@@ -6762,7 +6762,7 @@
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
     </row>
-    <row r="391" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="13"/>
       <c r="B391" s="6"/>
       <c r="C391" s="6"/>
@@ -6776,7 +6776,7 @@
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
     </row>
-    <row r="392" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="13"/>
       <c r="B392" s="6"/>
       <c r="C392" s="6"/>
@@ -6790,7 +6790,7 @@
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
     </row>
-    <row r="393" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="13"/>
       <c r="B393" s="6"/>
       <c r="C393" s="6"/>
@@ -6804,7 +6804,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
     </row>
-    <row r="394" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="13"/>
       <c r="B394" s="6"/>
       <c r="C394" s="6"/>
@@ -6818,7 +6818,7 @@
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
     </row>
-    <row r="395" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="13"/>
       <c r="B395" s="6"/>
       <c r="C395" s="6"/>
@@ -6832,7 +6832,7 @@
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
     </row>
-    <row r="396" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="13"/>
       <c r="B396" s="6"/>
       <c r="C396" s="6"/>
@@ -6846,7 +6846,7 @@
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
     </row>
-    <row r="397" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="13"/>
       <c r="B397" s="6"/>
       <c r="C397" s="6"/>
@@ -6860,7 +6860,7 @@
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
     </row>
-    <row r="398" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="13"/>
       <c r="B398" s="6"/>
       <c r="C398" s="6"/>
@@ -6874,7 +6874,7 @@
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
     </row>
-    <row r="399" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="13"/>
       <c r="B399" s="6"/>
       <c r="C399" s="6"/>
@@ -6888,7 +6888,7 @@
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
     </row>
-    <row r="400" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="13"/>
       <c r="B400" s="6"/>
       <c r="C400" s="6"/>
@@ -6902,7 +6902,7 @@
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
     </row>
-    <row r="401" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="13"/>
       <c r="B401" s="6"/>
       <c r="C401" s="6"/>
@@ -6916,7 +6916,7 @@
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
     </row>
-    <row r="402" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="13"/>
       <c r="B402" s="6"/>
       <c r="C402" s="6"/>
@@ -6930,7 +6930,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
     </row>
-    <row r="403" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="13"/>
       <c r="B403" s="6"/>
       <c r="C403" s="6"/>
@@ -6944,7 +6944,7 @@
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
     </row>
-    <row r="404" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="13"/>
       <c r="B404" s="6"/>
       <c r="C404" s="6"/>
@@ -6958,7 +6958,7 @@
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
     </row>
-    <row r="405" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="13"/>
       <c r="B405" s="6"/>
       <c r="C405" s="6"/>
@@ -6972,7 +6972,7 @@
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
     </row>
-    <row r="406" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="13"/>
       <c r="B406" s="6"/>
       <c r="C406" s="6"/>
@@ -6986,7 +6986,7 @@
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
     </row>
-    <row r="407" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="13"/>
       <c r="B407" s="6"/>
       <c r="C407" s="6"/>
@@ -7000,7 +7000,7 @@
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
     </row>
-    <row r="408" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="13"/>
       <c r="B408" s="6"/>
       <c r="C408" s="6"/>
@@ -7014,7 +7014,7 @@
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
     </row>
-    <row r="409" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="13"/>
       <c r="B409" s="6"/>
       <c r="C409" s="6"/>
@@ -7028,7 +7028,7 @@
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
     </row>
-    <row r="410" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="13"/>
       <c r="B410" s="6"/>
       <c r="C410" s="6"/>
@@ -7042,7 +7042,7 @@
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
     </row>
-    <row r="411" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="13"/>
       <c r="B411" s="6"/>
       <c r="C411" s="6"/>
@@ -7056,7 +7056,7 @@
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
     </row>
-    <row r="412" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="13"/>
       <c r="B412" s="6"/>
       <c r="C412" s="6"/>
@@ -7070,7 +7070,7 @@
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
     </row>
-    <row r="413" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="13"/>
       <c r="B413" s="6"/>
       <c r="C413" s="6"/>
@@ -7084,7 +7084,7 @@
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
     </row>
-    <row r="414" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="13"/>
       <c r="B414" s="6"/>
       <c r="C414" s="6"/>
@@ -7098,7 +7098,7 @@
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
     </row>
-    <row r="415" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="13"/>
       <c r="B415" s="6"/>
       <c r="C415" s="6"/>
@@ -7112,7 +7112,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
     </row>
-    <row r="416" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="13"/>
       <c r="B416" s="6"/>
       <c r="C416" s="6"/>
@@ -7126,7 +7126,7 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
     </row>
-    <row r="417" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="13"/>
       <c r="B417" s="6"/>
       <c r="C417" s="6"/>
@@ -7140,7 +7140,7 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
     </row>
-    <row r="418" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="13"/>
       <c r="B418" s="6"/>
       <c r="C418" s="6"/>
@@ -7154,7 +7154,7 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
     </row>
-    <row r="419" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="13"/>
       <c r="B419" s="6"/>
       <c r="C419" s="6"/>
@@ -7168,7 +7168,7 @@
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
     </row>
-    <row r="420" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="13"/>
       <c r="B420" s="6"/>
       <c r="C420" s="6"/>
@@ -7182,7 +7182,7 @@
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
     </row>
-    <row r="421" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="13"/>
       <c r="B421" s="6"/>
       <c r="C421" s="6"/>
@@ -7196,7 +7196,7 @@
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
     </row>
-    <row r="422" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="13"/>
       <c r="B422" s="6"/>
       <c r="C422" s="6"/>
@@ -7210,7 +7210,7 @@
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
     </row>
-    <row r="423" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="13"/>
       <c r="B423" s="6"/>
       <c r="C423" s="6"/>
@@ -7224,7 +7224,7 @@
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
     </row>
-    <row r="424" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="13"/>
       <c r="B424" s="6"/>
       <c r="C424" s="6"/>
@@ -7238,7 +7238,7 @@
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
     </row>
-    <row r="425" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="13"/>
       <c r="B425" s="6"/>
       <c r="C425" s="6"/>
@@ -7252,7 +7252,7 @@
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
     </row>
-    <row r="426" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="13"/>
       <c r="B426" s="6"/>
       <c r="C426" s="6"/>
@@ -7266,7 +7266,7 @@
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
     </row>
-    <row r="427" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="13"/>
       <c r="B427" s="6"/>
       <c r="C427" s="6"/>
@@ -7280,7 +7280,7 @@
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
     </row>
-    <row r="428" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="13"/>
       <c r="B428" s="6"/>
       <c r="C428" s="6"/>
@@ -7294,7 +7294,7 @@
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
     </row>
-    <row r="429" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="13"/>
       <c r="B429" s="6"/>
       <c r="C429" s="6"/>
@@ -7308,7 +7308,7 @@
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
     </row>
-    <row r="430" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="13"/>
       <c r="B430" s="6"/>
       <c r="C430" s="6"/>
@@ -7322,7 +7322,7 @@
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
     </row>
-    <row r="431" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="13"/>
       <c r="B431" s="6"/>
       <c r="C431" s="6"/>
@@ -7336,7 +7336,7 @@
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
     </row>
-    <row r="432" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="13"/>
       <c r="B432" s="6"/>
       <c r="C432" s="6"/>
@@ -7350,7 +7350,7 @@
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
     </row>
-    <row r="433" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="13"/>
       <c r="B433" s="6"/>
       <c r="C433" s="6"/>
@@ -7364,7 +7364,7 @@
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
     </row>
-    <row r="434" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="13"/>
       <c r="B434" s="6"/>
       <c r="C434" s="6"/>
@@ -7378,7 +7378,7 @@
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
     </row>
-    <row r="435" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="13"/>
       <c r="B435" s="6"/>
       <c r="C435" s="6"/>
@@ -7392,7 +7392,7 @@
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
     </row>
-    <row r="436" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="13"/>
       <c r="B436" s="6"/>
       <c r="C436" s="6"/>
@@ -7406,7 +7406,7 @@
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
     </row>
-    <row r="437" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="13"/>
       <c r="B437" s="6"/>
       <c r="C437" s="6"/>
@@ -7420,7 +7420,7 @@
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
     </row>
-    <row r="438" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="13"/>
       <c r="B438" s="6"/>
       <c r="C438" s="6"/>
@@ -7434,7 +7434,7 @@
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
     </row>
-    <row r="439" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="13"/>
       <c r="B439" s="6"/>
       <c r="C439" s="6"/>
@@ -7448,7 +7448,7 @@
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
     </row>
-    <row r="440" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="13"/>
       <c r="B440" s="6"/>
       <c r="C440" s="6"/>
@@ -7462,7 +7462,7 @@
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
     </row>
-    <row r="441" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="13"/>
       <c r="B441" s="6"/>
       <c r="C441" s="6"/>
@@ -7476,7 +7476,7 @@
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
     </row>
-    <row r="442" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="13"/>
       <c r="B442" s="6"/>
       <c r="C442" s="6"/>
@@ -7490,7 +7490,7 @@
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
     </row>
-    <row r="443" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="13"/>
       <c r="B443" s="6"/>
       <c r="C443" s="6"/>
@@ -7504,7 +7504,7 @@
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
     </row>
-    <row r="444" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="13"/>
       <c r="B444" s="6"/>
       <c r="C444" s="6"/>
@@ -7518,7 +7518,7 @@
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
     </row>
-    <row r="445" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="13"/>
       <c r="B445" s="6"/>
       <c r="C445" s="6"/>
@@ -7532,7 +7532,7 @@
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
     </row>
-    <row r="446" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="13"/>
       <c r="B446" s="6"/>
       <c r="C446" s="6"/>
@@ -7546,7 +7546,7 @@
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
     </row>
-    <row r="447" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="13"/>
       <c r="B447" s="6"/>
       <c r="C447" s="6"/>
@@ -7560,7 +7560,7 @@
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
     </row>
-    <row r="448" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="13"/>
       <c r="B448" s="6"/>
       <c r="C448" s="6"/>
@@ -7574,7 +7574,7 @@
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
     </row>
-    <row r="449" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="13"/>
       <c r="B449" s="6"/>
       <c r="C449" s="6"/>
@@ -7588,7 +7588,7 @@
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
     </row>
-    <row r="450" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="13"/>
       <c r="B450" s="6"/>
       <c r="C450" s="6"/>
@@ -7602,7 +7602,7 @@
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
     </row>
-    <row r="451" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="13"/>
       <c r="B451" s="6"/>
       <c r="C451" s="6"/>
@@ -7616,7 +7616,7 @@
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
     </row>
-    <row r="452" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="13"/>
       <c r="B452" s="6"/>
       <c r="C452" s="6"/>
@@ -7630,7 +7630,7 @@
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
     </row>
-    <row r="453" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="13"/>
       <c r="B453" s="6"/>
       <c r="C453" s="6"/>
@@ -7644,7 +7644,7 @@
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
     </row>
-    <row r="454" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="13"/>
       <c r="B454" s="6"/>
       <c r="C454" s="6"/>
@@ -7658,7 +7658,7 @@
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
     </row>
-    <row r="455" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="13"/>
       <c r="B455" s="6"/>
       <c r="C455" s="6"/>
@@ -7672,7 +7672,7 @@
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
     </row>
-    <row r="456" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="13"/>
       <c r="B456" s="6"/>
       <c r="C456" s="6"/>
@@ -7686,7 +7686,7 @@
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
     </row>
-    <row r="457" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="13"/>
       <c r="B457" s="6"/>
       <c r="C457" s="6"/>
@@ -7700,7 +7700,7 @@
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
     </row>
-    <row r="458" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="13"/>
       <c r="B458" s="6"/>
       <c r="C458" s="6"/>
@@ -7714,7 +7714,7 @@
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
     </row>
-    <row r="459" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="13"/>
       <c r="B459" s="6"/>
       <c r="C459" s="6"/>
@@ -7728,7 +7728,7 @@
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
     </row>
-    <row r="460" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="13"/>
       <c r="B460" s="6"/>
       <c r="C460" s="6"/>
@@ -7742,7 +7742,7 @@
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
     </row>
-    <row r="461" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="13"/>
       <c r="B461" s="6"/>
       <c r="C461" s="6"/>
@@ -7756,7 +7756,7 @@
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
     </row>
-    <row r="462" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="13"/>
       <c r="B462" s="6"/>
       <c r="C462" s="6"/>
@@ -7770,7 +7770,7 @@
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
     </row>
-    <row r="463" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="13"/>
       <c r="B463" s="6"/>
       <c r="C463" s="6"/>
@@ -7784,7 +7784,7 @@
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
     </row>
-    <row r="464" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="13"/>
       <c r="B464" s="6"/>
       <c r="C464" s="6"/>
@@ -7798,7 +7798,7 @@
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
     </row>
-    <row r="465" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="13"/>
       <c r="B465" s="6"/>
       <c r="C465" s="6"/>
@@ -7812,7 +7812,7 @@
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
     </row>
-    <row r="466" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="13"/>
       <c r="B466" s="6"/>
       <c r="C466" s="6"/>
@@ -7826,7 +7826,7 @@
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
     </row>
-    <row r="467" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="13"/>
       <c r="B467" s="6"/>
       <c r="C467" s="6"/>
@@ -7840,7 +7840,7 @@
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="13"/>
       <c r="B468" s="6"/>
       <c r="C468" s="6"/>
@@ -7854,7 +7854,7 @@
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
     </row>
-    <row r="469" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="13"/>
       <c r="B469" s="6"/>
       <c r="C469" s="6"/>
@@ -7868,7 +7868,7 @@
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
     </row>
-    <row r="470" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="13"/>
       <c r="B470" s="6"/>
       <c r="C470" s="6"/>
@@ -7882,7 +7882,7 @@
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
     </row>
-    <row r="471" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="13"/>
       <c r="B471" s="6"/>
       <c r="C471" s="6"/>
@@ -7896,7 +7896,7 @@
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
     </row>
-    <row r="472" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="13"/>
       <c r="B472" s="6"/>
       <c r="C472" s="6"/>
@@ -7910,7 +7910,7 @@
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
     </row>
-    <row r="473" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="13"/>
       <c r="B473" s="6"/>
       <c r="C473" s="6"/>
@@ -7924,7 +7924,7 @@
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
     </row>
-    <row r="474" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="13"/>
       <c r="B474" s="6"/>
       <c r="C474" s="6"/>
@@ -7938,7 +7938,7 @@
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
     </row>
-    <row r="475" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="13"/>
       <c r="B475" s="6"/>
       <c r="C475" s="6"/>
@@ -7952,7 +7952,7 @@
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
     </row>
-    <row r="476" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="13"/>
       <c r="B476" s="6"/>
       <c r="C476" s="6"/>
@@ -7966,7 +7966,7 @@
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
     </row>
-    <row r="477" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="13"/>
       <c r="B477" s="6"/>
       <c r="C477" s="6"/>
@@ -7980,7 +7980,7 @@
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
     </row>
-    <row r="478" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="13"/>
       <c r="B478" s="6"/>
       <c r="C478" s="6"/>
@@ -7994,7 +7994,7 @@
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
     </row>
-    <row r="479" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="13"/>
       <c r="B479" s="6"/>
       <c r="C479" s="6"/>
@@ -8008,7 +8008,7 @@
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
     </row>
-    <row r="480" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="13"/>
       <c r="B480" s="6"/>
       <c r="C480" s="6"/>
@@ -8022,7 +8022,7 @@
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
     </row>
-    <row r="481" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="13"/>
       <c r="B481" s="6"/>
       <c r="C481" s="6"/>
@@ -8036,7 +8036,7 @@
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
     </row>
-    <row r="482" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="13"/>
       <c r="B482" s="6"/>
       <c r="C482" s="6"/>
@@ -8050,7 +8050,7 @@
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
     </row>
-    <row r="483" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="13"/>
       <c r="B483" s="6"/>
       <c r="C483" s="6"/>
@@ -8064,7 +8064,7 @@
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
     </row>
-    <row r="484" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="13"/>
       <c r="B484" s="6"/>
       <c r="C484" s="6"/>
@@ -8078,7 +8078,7 @@
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
     </row>
-    <row r="485" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="13"/>
       <c r="B485" s="6"/>
       <c r="C485" s="6"/>
@@ -8092,7 +8092,7 @@
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
     </row>
-    <row r="486" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="13"/>
       <c r="B486" s="6"/>
       <c r="C486" s="6"/>
@@ -8106,7 +8106,7 @@
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
     </row>
-    <row r="487" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="13"/>
       <c r="B487" s="6"/>
       <c r="C487" s="6"/>
@@ -8120,7 +8120,7 @@
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
     </row>
-    <row r="488" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="13"/>
       <c r="B488" s="6"/>
       <c r="C488" s="6"/>
@@ -8134,7 +8134,7 @@
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
     </row>
-    <row r="489" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="13"/>
       <c r="B489" s="6"/>
       <c r="C489" s="6"/>
@@ -8148,7 +8148,7 @@
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
     </row>
-    <row r="490" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="13"/>
       <c r="B490" s="6"/>
       <c r="C490" s="6"/>
@@ -8162,7 +8162,7 @@
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
     </row>
-    <row r="491" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="13"/>
       <c r="B491" s="6"/>
       <c r="C491" s="6"/>
@@ -8176,7 +8176,7 @@
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
     </row>
-    <row r="492" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="13"/>
       <c r="B492" s="6"/>
       <c r="C492" s="6"/>
@@ -8190,7 +8190,7 @@
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
     </row>
-    <row r="493" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="13"/>
       <c r="B493" s="6"/>
       <c r="C493" s="6"/>
@@ -8204,7 +8204,7 @@
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
     </row>
-    <row r="494" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="13"/>
       <c r="B494" s="6"/>
       <c r="C494" s="6"/>
@@ -8218,7 +8218,7 @@
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
     </row>
-    <row r="495" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="13"/>
       <c r="B495" s="6"/>
       <c r="C495" s="6"/>
@@ -8232,7 +8232,7 @@
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
     </row>
-    <row r="496" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="13"/>
       <c r="B496" s="6"/>
       <c r="C496" s="6"/>
@@ -8246,7 +8246,7 @@
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
     </row>
-    <row r="497" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="13"/>
       <c r="B497" s="6"/>
       <c r="C497" s="6"/>
@@ -8260,7 +8260,7 @@
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
     </row>
-    <row r="498" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="13"/>
       <c r="B498" s="6"/>
       <c r="C498" s="6"/>
@@ -8274,7 +8274,7 @@
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
     </row>
-    <row r="499" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="13"/>
       <c r="B499" s="6"/>
       <c r="C499" s="6"/>
@@ -8288,7 +8288,7 @@
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
     </row>
-    <row r="500" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="13"/>
       <c r="B500" s="6"/>
       <c r="C500" s="6"/>
@@ -8302,7 +8302,7 @@
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
     </row>
-    <row r="501" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="13"/>
       <c r="B501" s="6"/>
       <c r="C501" s="6"/>
@@ -8316,7 +8316,7 @@
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
     </row>
-    <row r="502" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="13"/>
       <c r="B502" s="6"/>
       <c r="C502" s="6"/>
@@ -8330,7 +8330,7 @@
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
     </row>
-    <row r="503" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="13"/>
       <c r="B503" s="6"/>
       <c r="C503" s="6"/>
@@ -8344,7 +8344,7 @@
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
     </row>
-    <row r="504" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="13"/>
       <c r="B504" s="6"/>
       <c r="C504" s="6"/>
@@ -8358,7 +8358,7 @@
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
     </row>
-    <row r="505" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="13"/>
       <c r="B505" s="6"/>
       <c r="C505" s="6"/>
@@ -8372,7 +8372,7 @@
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
     </row>
-    <row r="506" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="13"/>
       <c r="B506" s="6"/>
       <c r="C506" s="6"/>
@@ -8386,7 +8386,7 @@
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
     </row>
-    <row r="507" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="13"/>
       <c r="B507" s="6"/>
       <c r="C507" s="6"/>
@@ -8400,7 +8400,7 @@
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
     </row>
-    <row r="508" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="13"/>
       <c r="B508" s="6"/>
       <c r="C508" s="6"/>
@@ -8414,7 +8414,7 @@
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
     </row>
-    <row r="509" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="13"/>
       <c r="B509" s="6"/>
       <c r="C509" s="6"/>
@@ -8428,7 +8428,7 @@
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
     </row>
-    <row r="510" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="13"/>
       <c r="B510" s="6"/>
       <c r="C510" s="6"/>
@@ -8442,7 +8442,7 @@
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
     </row>
-    <row r="511" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="13"/>
       <c r="B511" s="6"/>
       <c r="C511" s="6"/>
@@ -8456,7 +8456,7 @@
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
     </row>
-    <row r="512" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="13"/>
       <c r="B512" s="6"/>
       <c r="C512" s="6"/>
@@ -8470,7 +8470,7 @@
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
     </row>
-    <row r="513" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="13"/>
       <c r="B513" s="6"/>
       <c r="C513" s="6"/>
@@ -8484,7 +8484,7 @@
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
     </row>
-    <row r="514" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="13"/>
       <c r="B514" s="6"/>
       <c r="C514" s="6"/>
@@ -8498,7 +8498,7 @@
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
     </row>
-    <row r="515" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="13"/>
       <c r="B515" s="6"/>
       <c r="C515" s="6"/>
@@ -8512,7 +8512,7 @@
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
     </row>
-    <row r="516" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="13"/>
       <c r="B516" s="6"/>
       <c r="C516" s="6"/>
@@ -8526,7 +8526,7 @@
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
     </row>
-    <row r="517" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="13"/>
       <c r="B517" s="6"/>
       <c r="C517" s="6"/>
@@ -8540,7 +8540,7 @@
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
     </row>
-    <row r="518" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="13"/>
       <c r="B518" s="6"/>
       <c r="C518" s="6"/>
@@ -8554,7 +8554,7 @@
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
     </row>
-    <row r="519" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="13"/>
       <c r="B519" s="6"/>
       <c r="C519" s="6"/>
@@ -8568,7 +8568,7 @@
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
     </row>
-    <row r="520" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="13"/>
       <c r="B520" s="6"/>
       <c r="C520" s="6"/>
@@ -8582,7 +8582,7 @@
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
     </row>
-    <row r="521" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="13"/>
       <c r="B521" s="6"/>
       <c r="C521" s="6"/>
